--- a/Notas_EDO_IMPA_TECH.xlsx
+++ b/Notas_EDO_IMPA_TECH.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Teste 1" sheetId="1" state="visible" r:id="rId3"/>
@@ -14,6 +14,7 @@
     <sheet name="Lista 2" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Prova 1" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Média" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Teste Extra 1" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="112">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -377,7 +378,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -399,42 +399,36 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans&quot;"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Google Sans"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFC9211E"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFF10D0C"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -497,7 +491,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -547,6 +541,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -739,7 +737,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -748,13 +746,13 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -762,13 +760,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -776,7 +774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -784,7 +782,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -792,7 +790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -800,7 +798,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -808,7 +806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -816,7 +814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -824,7 +822,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -832,7 +830,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -840,13 +838,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -854,7 +852,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -862,7 +860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -870,7 +868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -878,7 +876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -886,7 +884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -894,7 +892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -902,7 +900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -910,7 +908,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -918,7 +916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -926,7 +924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -934,13 +932,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
@@ -948,7 +946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
@@ -956,7 +954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
@@ -964,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
@@ -972,7 +970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -980,7 +978,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -988,7 +986,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -996,7 +994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -1004,13 +1002,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -1018,7 +1016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -1026,7 +1024,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -1034,7 +1032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
@@ -1042,7 +1040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -1050,7 +1048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
@@ -1058,7 +1056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -1066,7 +1064,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -1074,7 +1072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -1082,7 +1080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
@@ -1090,7 +1088,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -1098,13 +1096,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
         <v>48</v>
       </c>
@@ -1112,7 +1110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
@@ -1120,7 +1118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>50</v>
       </c>
@@ -1128,7 +1126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
@@ -1136,7 +1134,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
         <v>52</v>
       </c>
@@ -1144,7 +1142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -1152,13 +1150,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
@@ -1166,7 +1164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>56</v>
       </c>
@@ -1174,7 +1172,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
@@ -1182,7 +1180,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -1190,7 +1188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
@@ -1198,7 +1196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>60</v>
       </c>
@@ -1206,7 +1204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
@@ -1214,7 +1212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>62</v>
       </c>
@@ -1222,7 +1220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -1230,13 +1228,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B64" s="4"/>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
@@ -1244,7 +1242,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>66</v>
       </c>
@@ -1252,7 +1250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -1260,7 +1258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
@@ -1268,13 +1266,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B69" s="4"/>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
         <v>70</v>
       </c>
@@ -1282,7 +1280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -1290,7 +1288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
@@ -1298,7 +1296,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -1306,7 +1304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
         <v>74</v>
       </c>
@@ -1314,7 +1312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
@@ -1322,7 +1320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
         <v>76</v>
       </c>
@@ -1330,7 +1328,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
@@ -1338,7 +1336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
         <v>78</v>
       </c>
@@ -1346,7 +1344,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -1376,7 +1374,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1385,13 +1383,13 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1399,13 +1397,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -1413,7 +1411,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -1421,7 +1419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1429,7 +1427,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -1437,7 +1435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -1445,7 +1443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -1453,7 +1451,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -1461,7 +1459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -1469,7 +1467,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -1477,13 +1475,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -1491,7 +1489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -1499,7 +1497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -1507,7 +1505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -1515,7 +1513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -1523,7 +1521,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -1531,7 +1529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -1539,7 +1537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -1547,7 +1545,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -1555,7 +1553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -1563,7 +1561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -1571,13 +1569,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
@@ -1585,7 +1583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
@@ -1593,7 +1591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
@@ -1601,7 +1599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
@@ -1609,7 +1607,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1617,7 +1615,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -1625,7 +1623,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -1633,7 +1631,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -1641,13 +1639,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -1655,7 +1653,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -1663,7 +1661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -1671,7 +1669,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
@@ -1679,7 +1677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -1687,7 +1685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
@@ -1695,7 +1693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -1703,7 +1701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -1711,7 +1709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -1719,7 +1717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
@@ -1727,7 +1725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -1735,7 +1733,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
@@ -1743,7 +1741,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
         <v>48</v>
       </c>
@@ -1751,7 +1749,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
@@ -1759,7 +1757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>50</v>
       </c>
@@ -1767,7 +1765,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
@@ -1775,7 +1773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
         <v>52</v>
       </c>
@@ -1783,7 +1781,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -1791,7 +1789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
@@ -1799,7 +1797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
@@ -1807,7 +1805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>56</v>
       </c>
@@ -1815,7 +1813,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
@@ -1823,7 +1821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -1831,7 +1829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
@@ -1839,7 +1837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>60</v>
       </c>
@@ -1847,7 +1845,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
@@ -1855,7 +1853,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>62</v>
       </c>
@@ -1863,7 +1861,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -1871,13 +1869,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B64" s="4"/>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
@@ -1885,7 +1883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>66</v>
       </c>
@@ -1893,7 +1891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -1901,7 +1899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
@@ -1909,13 +1907,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B69" s="4"/>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
         <v>70</v>
       </c>
@@ -1923,7 +1921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -1931,7 +1929,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
@@ -1939,7 +1937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -1947,7 +1945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
         <v>74</v>
       </c>
@@ -1955,7 +1953,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
@@ -1963,7 +1961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
         <v>76</v>
       </c>
@@ -1971,7 +1969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
@@ -1979,7 +1977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
         <v>78</v>
       </c>
@@ -1987,7 +1985,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -2021,7 +2019,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2044,7 +2042,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -2064,7 +2062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2088,7 +2086,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -2109,7 +2107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -2133,7 +2131,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -2157,7 +2155,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -2181,7 +2179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2205,7 +2203,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -2229,7 +2227,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -2253,7 +2251,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -2277,7 +2275,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -2301,7 +2299,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -2325,7 +2323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
@@ -2345,7 +2343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -2369,7 +2367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -2393,7 +2391,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -2417,7 +2415,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -2441,7 +2439,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -2465,7 +2463,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -2489,7 +2487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -2513,7 +2511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -2537,7 +2535,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -2561,7 +2559,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -2585,7 +2583,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -2609,7 +2607,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
@@ -2629,7 +2627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
@@ -2653,7 +2651,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
@@ -2677,7 +2675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
@@ -2701,7 +2699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
@@ -2725,7 +2723,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -2749,7 +2747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -2773,7 +2771,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -2797,7 +2795,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -2821,7 +2819,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
@@ -2841,7 +2839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -2865,7 +2863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -2889,7 +2887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -2913,7 +2911,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
@@ -2937,7 +2935,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -2961,7 +2959,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
@@ -2985,7 +2983,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -3009,7 +3007,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -3033,7 +3031,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -3057,7 +3055,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
@@ -3081,7 +3079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -3105,7 +3103,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
@@ -3125,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
         <v>48</v>
       </c>
@@ -3149,7 +3147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
@@ -3173,7 +3171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>50</v>
       </c>
@@ -3197,7 +3195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
@@ -3221,7 +3219,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
         <v>52</v>
       </c>
@@ -3245,7 +3243,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -3269,7 +3267,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
@@ -3293,7 +3291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
@@ -3317,7 +3315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>56</v>
       </c>
@@ -3341,7 +3339,7 @@
         <v>9.3</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
@@ -3365,7 +3363,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -3389,7 +3387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
@@ -3413,7 +3411,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>60</v>
       </c>
@@ -3437,7 +3435,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
@@ -3461,7 +3459,7 @@
         <v>8.8</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>62</v>
       </c>
@@ -3485,7 +3483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -3509,7 +3507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>64</v>
       </c>
@@ -3529,7 +3527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
@@ -3553,7 +3551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>66</v>
       </c>
@@ -3577,7 +3575,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -3601,7 +3599,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
@@ -3625,7 +3623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
@@ -3645,7 +3643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
         <v>70</v>
       </c>
@@ -3669,7 +3667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -3693,7 +3691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
@@ -3717,7 +3715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -3741,7 +3739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
         <v>74</v>
       </c>
@@ -3765,7 +3763,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
@@ -3789,7 +3787,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
         <v>76</v>
       </c>
@@ -3813,7 +3811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
@@ -3837,7 +3835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
         <v>78</v>
       </c>
@@ -3861,7 +3859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -3911,7 +3909,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.88"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3940,7 +3938,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -3956,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -3968,7 +3966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -3981,7 +3979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -3993,7 +3991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -4005,7 +4003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -4017,7 +4015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -4029,7 +4027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -4041,7 +4039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -4053,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -4065,7 +4063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -4077,7 +4075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -4089,7 +4087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
@@ -4101,7 +4099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -4113,7 +4111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -4125,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -4137,7 +4135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -4149,7 +4147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -4161,7 +4159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -4173,7 +4171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -4185,7 +4183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -4197,7 +4195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -4209,7 +4207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -4221,7 +4219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -4233,7 +4231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
@@ -4245,7 +4243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
@@ -4257,7 +4255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
@@ -4269,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
@@ -4281,7 +4279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
@@ -4293,7 +4291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -4305,7 +4303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -4317,7 +4315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -4329,7 +4327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -4341,7 +4339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
@@ -4353,7 +4351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -4365,7 +4363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -4377,7 +4375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -4389,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
@@ -4401,7 +4399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -4413,7 +4411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
@@ -4425,7 +4423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -4437,7 +4435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -4449,7 +4447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -4461,7 +4459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
@@ -4473,7 +4471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -4485,7 +4483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
@@ -4497,7 +4495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
         <v>48</v>
       </c>
@@ -4509,7 +4507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
@@ -4521,7 +4519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>50</v>
       </c>
@@ -4533,7 +4531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
@@ -4545,7 +4543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
         <v>52</v>
       </c>
@@ -4557,7 +4555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -4569,7 +4567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
@@ -4581,7 +4579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
@@ -4593,7 +4591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>56</v>
       </c>
@@ -4605,7 +4603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
@@ -4617,7 +4615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -4629,7 +4627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
@@ -4641,7 +4639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>60</v>
       </c>
@@ -4653,7 +4651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
@@ -4665,7 +4663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>62</v>
       </c>
@@ -4677,7 +4675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -4689,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>64</v>
       </c>
@@ -4701,7 +4699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
@@ -4713,7 +4711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>66</v>
       </c>
@@ -4725,7 +4723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -4737,7 +4735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
@@ -4749,7 +4747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
@@ -4761,7 +4759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
         <v>70</v>
       </c>
@@ -4773,7 +4771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -4785,7 +4783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
@@ -4797,7 +4795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -4809,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
         <v>74</v>
       </c>
@@ -4821,7 +4819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
@@ -4833,7 +4831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
         <v>76</v>
       </c>
@@ -4845,7 +4843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
@@ -4857,7 +4855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
         <v>78</v>
       </c>
@@ -4869,7 +4867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -4904,7 +4902,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4912,7 +4910,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -4920,7 +4918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -4928,7 +4926,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -4936,7 +4934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -4944,7 +4942,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -4952,7 +4950,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -4960,7 +4958,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -4968,7 +4966,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -4976,7 +4974,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -4984,7 +4982,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -4992,7 +4990,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -5000,7 +4998,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -5008,7 +5006,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
@@ -5016,7 +5014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -5024,7 +5022,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -5032,7 +5030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -5040,7 +5038,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -5048,7 +5046,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -5056,7 +5054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -5064,7 +5062,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -5072,7 +5070,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -5080,7 +5078,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -5088,7 +5086,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -5096,7 +5094,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -5104,7 +5102,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
@@ -5112,7 +5110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
@@ -5120,7 +5118,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
@@ -5128,7 +5126,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>96</v>
       </c>
@@ -5136,7 +5134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
@@ -5144,7 +5142,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -5152,7 +5150,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -5160,7 +5158,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -5168,7 +5166,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -5176,7 +5174,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
@@ -5184,7 +5182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -5192,7 +5190,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -5200,7 +5198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -5208,7 +5206,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
@@ -5216,7 +5214,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -5224,7 +5222,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
@@ -5232,7 +5230,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -5240,7 +5238,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -5248,7 +5246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -5256,7 +5254,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
@@ -5264,7 +5262,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -5272,7 +5270,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
@@ -5280,7 +5278,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
         <v>48</v>
       </c>
@@ -5288,7 +5286,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
@@ -5296,7 +5294,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>50</v>
       </c>
@@ -5304,7 +5302,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
@@ -5312,7 +5310,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
         <v>52</v>
       </c>
@@ -5320,7 +5318,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -5328,7 +5326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
@@ -5336,7 +5334,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
@@ -5344,7 +5342,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>56</v>
       </c>
@@ -5352,7 +5350,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
@@ -5360,7 +5358,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -5368,7 +5366,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
@@ -5376,7 +5374,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>60</v>
       </c>
@@ -5384,7 +5382,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
@@ -5392,7 +5390,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>62</v>
       </c>
@@ -5400,7 +5398,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -5408,7 +5406,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>64</v>
       </c>
@@ -5416,7 +5414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
@@ -5424,7 +5422,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>66</v>
       </c>
@@ -5432,7 +5430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -5440,7 +5438,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
@@ -5448,7 +5446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
@@ -5456,7 +5454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
         <v>70</v>
       </c>
@@ -5464,7 +5462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -5472,7 +5470,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
@@ -5480,7 +5478,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -5488,7 +5486,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
         <v>74</v>
       </c>
@@ -5496,7 +5494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
@@ -5504,7 +5502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
         <v>76</v>
       </c>
@@ -5512,7 +5510,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
@@ -5520,7 +5518,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
         <v>78</v>
       </c>
@@ -5528,7 +5526,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -5536,22 +5534,22 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B80" s="2" t="n">
         <f aca="false">AVERAGE(B2:B79)</f>
-        <v>38.03846154</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>38.0384615384615</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B81" s="2" t="n">
         <f aca="false">STDEV(B2:B79)</f>
-        <v>26.15609601</v>
+        <v>26.1560960130016</v>
       </c>
     </row>
   </sheetData>
@@ -5579,7 +5577,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="25.25"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5617,7 +5615,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -5664,7 +5662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
@@ -5713,7 +5711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5760,7 +5758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
@@ -5808,7 +5806,7 @@
         <v>5.1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
@@ -5857,7 +5855,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
@@ -5906,7 +5904,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
@@ -5955,7 +5953,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
@@ -6003,7 +6001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>10</v>
       </c>
@@ -6052,7 +6050,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>11</v>
       </c>
@@ -6101,7 +6099,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>12</v>
       </c>
@@ -6149,7 +6147,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>13</v>
       </c>
@@ -6198,7 +6196,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
         <v>14</v>
       </c>
@@ -6245,7 +6243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
         <v>15</v>
       </c>
@@ -6294,7 +6292,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
         <v>16</v>
       </c>
@@ -6343,7 +6341,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
         <v>17</v>
       </c>
@@ -6391,7 +6389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
         <v>18</v>
       </c>
@@ -6440,7 +6438,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
         <v>19</v>
       </c>
@@ -6489,7 +6487,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
         <v>20</v>
       </c>
@@ -6538,7 +6536,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
         <v>21</v>
       </c>
@@ -6587,7 +6585,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
         <v>22</v>
       </c>
@@ -6635,7 +6633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
         <v>23</v>
       </c>
@@ -6684,7 +6682,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
         <v>24</v>
       </c>
@@ -6733,7 +6731,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
         <v>25</v>
       </c>
@@ -6782,7 +6780,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
         <v>26</v>
       </c>
@@ -6829,7 +6827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
         <v>27</v>
       </c>
@@ -6878,7 +6876,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
         <v>28</v>
       </c>
@@ -6927,7 +6925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
         <v>96</v>
       </c>
@@ -6976,7 +6974,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
         <v>30</v>
       </c>
@@ -7025,7 +7023,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
         <v>31</v>
       </c>
@@ -7073,7 +7071,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
         <v>32</v>
       </c>
@@ -7122,7 +7120,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
         <v>33</v>
       </c>
@@ -7171,7 +7169,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
         <v>34</v>
       </c>
@@ -7220,7 +7218,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
         <v>35</v>
       </c>
@@ -7267,7 +7265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
         <v>36</v>
       </c>
@@ -7315,7 +7313,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
         <v>37</v>
       </c>
@@ -7364,7 +7362,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
         <v>38</v>
       </c>
@@ -7413,7 +7411,7 @@
         <v>9.7</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
         <v>39</v>
       </c>
@@ -7460,7 +7458,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
         <v>40</v>
       </c>
@@ -7509,7 +7507,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
         <v>41</v>
       </c>
@@ -7558,7 +7556,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
         <v>42</v>
       </c>
@@ -7607,7 +7605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
         <v>43</v>
       </c>
@@ -7656,7 +7654,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
         <v>44</v>
       </c>
@@ -7705,7 +7703,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
         <v>45</v>
       </c>
@@ -7754,7 +7752,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
         <v>46</v>
       </c>
@@ -7803,7 +7801,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
         <v>47</v>
       </c>
@@ -7851,7 +7849,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
         <v>48</v>
       </c>
@@ -7900,7 +7898,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
         <v>49</v>
       </c>
@@ -7948,7 +7946,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
         <v>50</v>
       </c>
@@ -7997,7 +7995,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
         <v>51</v>
       </c>
@@ -8046,7 +8044,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
         <v>52</v>
       </c>
@@ -8095,7 +8093,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
         <v>53</v>
       </c>
@@ -8144,7 +8142,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
         <v>54</v>
       </c>
@@ -8194,7 +8192,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
         <v>55</v>
       </c>
@@ -8243,7 +8241,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
         <v>56</v>
       </c>
@@ -8292,7 +8290,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
         <v>57</v>
       </c>
@@ -8341,7 +8339,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
         <v>58</v>
       </c>
@@ -8390,7 +8388,7 @@
         <v>8.2</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
         <v>59</v>
       </c>
@@ -8439,7 +8437,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
         <v>60</v>
       </c>
@@ -8488,7 +8486,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9" t="s">
         <v>61</v>
       </c>
@@ -8537,7 +8535,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
         <v>62</v>
       </c>
@@ -8586,7 +8584,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
         <v>63</v>
       </c>
@@ -8635,7 +8633,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
         <v>64</v>
       </c>
@@ -8682,7 +8680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
         <v>65</v>
       </c>
@@ -8731,7 +8729,7 @@
         <v>9.7</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
         <v>66</v>
       </c>
@@ -8780,7 +8778,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
         <v>67</v>
       </c>
@@ -8829,7 +8827,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
         <v>68</v>
       </c>
@@ -8870,15 +8868,14 @@
         <v>9.5</v>
       </c>
       <c r="K68" s="2" t="n">
-        <f aca="false">'Prova 1'!B68/10</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L68" s="8" t="n">
         <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D68*0.2,G68*0.05,J68*0.05,K68)*(6/5))*(20/43) + (138/43)))/10</f>
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
         <v>69</v>
       </c>
@@ -8925,7 +8922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="9" t="s">
         <v>70</v>
       </c>
@@ -8974,7 +8971,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="9" t="s">
         <v>71</v>
       </c>
@@ -9023,7 +9020,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
         <v>72</v>
       </c>
@@ -9072,7 +9069,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
         <v>73</v>
       </c>
@@ -9121,7 +9118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="s">
         <v>74</v>
       </c>
@@ -9169,7 +9166,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
         <v>75</v>
       </c>
@@ -9217,7 +9214,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
         <v>76</v>
       </c>
@@ -9266,7 +9263,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
         <v>77</v>
       </c>
@@ -9315,7 +9312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
         <v>78</v>
       </c>
@@ -9364,7 +9361,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
         <v>79</v>
       </c>
@@ -9422,4 +9419,643 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B79"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.63"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Notas_EDO_IMPA_TECH.xlsx
+++ b/Notas_EDO_IMPA_TECH.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Teste 1" sheetId="1" state="visible" r:id="rId3"/>
@@ -15,6 +15,7 @@
     <sheet name="Prova 1" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Média" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Teste Extra 1" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Teste Extra 2" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="113">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -356,6 +357,9 @@
   </si>
   <si>
     <t xml:space="preserve">AV1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS: +0.7 na AV2 (se nota(AV2) &gt; 9.7, nota final = 10) </t>
   </si>
   <si>
     <t xml:space="preserve">OBS: +0.7 na AV2</t>
@@ -378,6 +382,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -399,36 +404,42 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans&quot;"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Google Sans"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFC9211E"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFF10D0C"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -491,7 +502,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -541,10 +552,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -737,7 +744,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -746,13 +753,13 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -760,13 +767,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -774,7 +781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -782,7 +789,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -790,7 +797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -798,7 +805,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -806,7 +813,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -814,7 +821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -822,7 +829,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -830,7 +837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -838,13 +845,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -852,7 +859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -860,7 +867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -868,7 +875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -876,7 +883,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -884,7 +891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -892,7 +899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -900,7 +907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -908,7 +915,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -916,7 +923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -924,7 +931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -932,13 +939,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
@@ -946,7 +953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
@@ -954,7 +961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
@@ -962,7 +969,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
@@ -970,7 +977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -978,7 +985,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -986,7 +993,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -994,7 +1001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -1002,13 +1009,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -1016,7 +1023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -1024,7 +1031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -1032,7 +1039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
@@ -1040,7 +1047,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -1048,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
@@ -1056,7 +1063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -1064,7 +1071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -1072,7 +1079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -1080,7 +1087,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
@@ -1088,7 +1095,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -1096,13 +1103,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
         <v>48</v>
       </c>
@@ -1110,7 +1117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
@@ -1118,7 +1125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>50</v>
       </c>
@@ -1126,7 +1133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
@@ -1134,7 +1141,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
         <v>52</v>
       </c>
@@ -1142,7 +1149,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -1150,13 +1157,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
@@ -1164,7 +1171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>56</v>
       </c>
@@ -1172,7 +1179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
@@ -1180,7 +1187,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -1188,7 +1195,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
@@ -1196,7 +1203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>60</v>
       </c>
@@ -1204,7 +1211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
@@ -1212,7 +1219,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>62</v>
       </c>
@@ -1220,7 +1227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -1228,13 +1235,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B64" s="4"/>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
@@ -1242,7 +1249,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>66</v>
       </c>
@@ -1250,7 +1257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -1258,7 +1265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
@@ -1266,13 +1273,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B69" s="4"/>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
         <v>70</v>
       </c>
@@ -1280,7 +1287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -1288,7 +1295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
@@ -1296,7 +1303,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -1304,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
         <v>74</v>
       </c>
@@ -1312,7 +1319,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
@@ -1320,7 +1327,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
         <v>76</v>
       </c>
@@ -1328,7 +1335,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
@@ -1336,7 +1343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
         <v>78</v>
       </c>
@@ -1344,7 +1351,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -1374,7 +1381,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1383,13 +1390,13 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1397,13 +1404,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -1411,7 +1418,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -1419,7 +1426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1427,7 +1434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -1435,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -1443,7 +1450,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -1451,7 +1458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -1459,7 +1466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -1467,7 +1474,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -1475,13 +1482,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -1489,7 +1496,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -1497,7 +1504,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -1505,7 +1512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -1513,7 +1520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -1521,7 +1528,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -1529,7 +1536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -1537,7 +1544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -1545,7 +1552,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -1553,7 +1560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -1561,7 +1568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -1569,13 +1576,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
@@ -1583,7 +1590,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
@@ -1591,7 +1598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
@@ -1599,7 +1606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
@@ -1607,7 +1614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1615,7 +1622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -1623,7 +1630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -1631,7 +1638,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -1639,13 +1646,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -1653,7 +1660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -1661,7 +1668,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -1669,7 +1676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
@@ -1677,7 +1684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -1685,7 +1692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
@@ -1693,7 +1700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -1701,7 +1708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -1709,7 +1716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -1717,7 +1724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
@@ -1725,7 +1732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -1733,7 +1740,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
@@ -1741,7 +1748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
         <v>48</v>
       </c>
@@ -1749,7 +1756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
@@ -1757,7 +1764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>50</v>
       </c>
@@ -1765,7 +1772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
@@ -1773,7 +1780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
         <v>52</v>
       </c>
@@ -1781,7 +1788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -1789,7 +1796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
@@ -1797,7 +1804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
@@ -1805,7 +1812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>56</v>
       </c>
@@ -1813,7 +1820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
@@ -1821,7 +1828,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -1829,7 +1836,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
@@ -1837,7 +1844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>60</v>
       </c>
@@ -1845,7 +1852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
@@ -1853,7 +1860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>62</v>
       </c>
@@ -1861,7 +1868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -1869,13 +1876,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B64" s="4"/>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
@@ -1883,7 +1890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>66</v>
       </c>
@@ -1891,7 +1898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -1899,7 +1906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
@@ -1907,13 +1914,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B69" s="4"/>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
         <v>70</v>
       </c>
@@ -1921,7 +1928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -1929,7 +1936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
@@ -1937,7 +1944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -1945,7 +1952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
         <v>74</v>
       </c>
@@ -1953,7 +1960,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
@@ -1961,7 +1968,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
         <v>76</v>
       </c>
@@ -1969,7 +1976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
@@ -1977,7 +1984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
         <v>78</v>
       </c>
@@ -1985,7 +1992,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -2019,7 +2026,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2042,7 +2049,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -2062,7 +2069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2086,7 +2093,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -2107,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -2131,7 +2138,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -2155,7 +2162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -2179,7 +2186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2203,7 +2210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -2227,7 +2234,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -2251,7 +2258,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -2275,7 +2282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -2299,7 +2306,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -2323,7 +2330,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
@@ -2343,7 +2350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -2367,7 +2374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -2391,7 +2398,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -2415,7 +2422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -2439,7 +2446,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -2463,7 +2470,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -2487,7 +2494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -2511,7 +2518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -2535,7 +2542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -2559,7 +2566,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -2583,7 +2590,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -2607,7 +2614,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
@@ -2627,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
@@ -2651,7 +2658,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
@@ -2675,7 +2682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
@@ -2699,7 +2706,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
@@ -2723,7 +2730,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -2747,7 +2754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -2771,7 +2778,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -2795,7 +2802,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -2819,7 +2826,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
@@ -2839,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -2863,7 +2870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -2887,7 +2894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -2911,7 +2918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
@@ -2935,7 +2942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -2959,7 +2966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
@@ -2983,7 +2990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -3007,7 +3014,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -3031,7 +3038,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -3055,7 +3062,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
@@ -3079,7 +3086,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -3103,7 +3110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
@@ -3123,7 +3130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
         <v>48</v>
       </c>
@@ -3147,7 +3154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
@@ -3171,7 +3178,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>50</v>
       </c>
@@ -3195,7 +3202,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
@@ -3219,7 +3226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
         <v>52</v>
       </c>
@@ -3243,7 +3250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -3267,7 +3274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
@@ -3291,7 +3298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
@@ -3315,7 +3322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>56</v>
       </c>
@@ -3339,7 +3346,7 @@
         <v>9.3</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
@@ -3363,7 +3370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -3387,7 +3394,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
@@ -3411,7 +3418,7 @@
         <v>9.8</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>60</v>
       </c>
@@ -3435,7 +3442,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
@@ -3459,7 +3466,7 @@
         <v>8.8</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>62</v>
       </c>
@@ -3483,7 +3490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -3507,7 +3514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>64</v>
       </c>
@@ -3527,7 +3534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
@@ -3551,7 +3558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>66</v>
       </c>
@@ -3575,7 +3582,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -3599,7 +3606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
@@ -3623,7 +3630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
@@ -3643,7 +3650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
         <v>70</v>
       </c>
@@ -3667,7 +3674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -3691,7 +3698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
@@ -3715,7 +3722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -3739,7 +3746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
         <v>74</v>
       </c>
@@ -3763,7 +3770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
@@ -3787,7 +3794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
         <v>76</v>
       </c>
@@ -3811,7 +3818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
@@ -3835,7 +3842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
         <v>78</v>
       </c>
@@ -3859,7 +3866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -3909,7 +3916,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.88"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3938,7 +3945,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -3954,7 +3961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -3966,7 +3973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -3979,7 +3986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -3991,7 +3998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -4003,7 +4010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -4015,7 +4022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -4027,7 +4034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -4039,7 +4046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -4051,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -4063,7 +4070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -4075,7 +4082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -4087,7 +4094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
@@ -4099,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -4111,7 +4118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -4123,7 +4130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -4135,7 +4142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -4147,7 +4154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -4159,7 +4166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -4171,7 +4178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -4183,7 +4190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -4195,7 +4202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -4207,7 +4214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -4219,7 +4226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -4231,7 +4238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
@@ -4243,7 +4250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
@@ -4255,7 +4262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
@@ -4267,7 +4274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>29</v>
       </c>
@@ -4279,7 +4286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
@@ -4291,7 +4298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -4303,7 +4310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -4315,7 +4322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -4327,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -4339,7 +4346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
@@ -4351,7 +4358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -4363,7 +4370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -4375,7 +4382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -4387,7 +4394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
@@ -4399,7 +4406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -4411,7 +4418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
@@ -4423,7 +4430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -4435,7 +4442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -4447,7 +4454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -4459,7 +4466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
@@ -4471,7 +4478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -4483,7 +4490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
@@ -4495,7 +4502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
         <v>48</v>
       </c>
@@ -4507,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
@@ -4519,7 +4526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>50</v>
       </c>
@@ -4531,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
@@ -4543,7 +4550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
         <v>52</v>
       </c>
@@ -4555,7 +4562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -4567,7 +4574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
@@ -4579,7 +4586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
@@ -4591,7 +4598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>56</v>
       </c>
@@ -4603,7 +4610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
@@ -4615,7 +4622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -4627,7 +4634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
@@ -4639,7 +4646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>60</v>
       </c>
@@ -4651,7 +4658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
@@ -4663,7 +4670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>62</v>
       </c>
@@ -4675,7 +4682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -4687,7 +4694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>64</v>
       </c>
@@ -4699,7 +4706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
@@ -4711,7 +4718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>66</v>
       </c>
@@ -4723,7 +4730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -4735,7 +4742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
@@ -4747,7 +4754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
@@ -4759,7 +4766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
         <v>70</v>
       </c>
@@ -4771,7 +4778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -4783,7 +4790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
@@ -4795,7 +4802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -4807,7 +4814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
         <v>74</v>
       </c>
@@ -4819,7 +4826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
@@ -4831,7 +4838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
         <v>76</v>
       </c>
@@ -4843,7 +4850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
@@ -4855,7 +4862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
         <v>78</v>
       </c>
@@ -4867,7 +4874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -4902,7 +4909,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4910,7 +4917,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -4918,7 +4925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -4926,7 +4933,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -4934,7 +4941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -4942,7 +4949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -4950,7 +4957,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -4958,7 +4965,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -4966,7 +4973,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -4974,7 +4981,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -4982,7 +4989,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
@@ -4990,7 +4997,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -4998,7 +5005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -5006,7 +5013,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
@@ -5014,7 +5021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -5022,7 +5029,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
@@ -5030,7 +5037,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -5038,7 +5045,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -5046,7 +5053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -5054,7 +5061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
@@ -5062,7 +5069,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
@@ -5070,7 +5077,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>22</v>
       </c>
@@ -5078,7 +5085,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>23</v>
       </c>
@@ -5086,7 +5093,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
@@ -5094,7 +5101,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
@@ -5102,7 +5109,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
@@ -5110,7 +5117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
@@ -5118,7 +5125,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>28</v>
       </c>
@@ -5126,7 +5133,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>96</v>
       </c>
@@ -5134,7 +5141,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
         <v>30</v>
       </c>
@@ -5142,7 +5149,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -5150,7 +5157,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>32</v>
       </c>
@@ -5158,7 +5165,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>33</v>
       </c>
@@ -5166,7 +5173,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -5174,7 +5181,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>35</v>
       </c>
@@ -5182,7 +5189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -5190,7 +5197,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
@@ -5198,7 +5205,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -5206,7 +5213,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
@@ -5214,7 +5221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
@@ -5222,7 +5229,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
@@ -5230,7 +5237,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
@@ -5238,7 +5245,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -5246,7 +5253,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -5254,7 +5261,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
         <v>45</v>
       </c>
@@ -5262,7 +5269,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -5270,7 +5277,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
@@ -5278,7 +5285,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
         <v>48</v>
       </c>
@@ -5286,7 +5293,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
         <v>49</v>
       </c>
@@ -5294,7 +5301,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
         <v>50</v>
       </c>
@@ -5302,7 +5309,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
         <v>51</v>
       </c>
@@ -5310,7 +5317,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
         <v>52</v>
       </c>
@@ -5318,7 +5325,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
         <v>53</v>
       </c>
@@ -5326,7 +5333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
@@ -5334,7 +5341,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
         <v>55</v>
       </c>
@@ -5342,7 +5349,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
         <v>56</v>
       </c>
@@ -5350,7 +5357,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
         <v>57</v>
       </c>
@@ -5358,7 +5365,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
         <v>58</v>
       </c>
@@ -5366,7 +5373,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
         <v>59</v>
       </c>
@@ -5374,7 +5381,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
         <v>60</v>
       </c>
@@ -5382,7 +5389,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
         <v>61</v>
       </c>
@@ -5390,7 +5397,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
         <v>62</v>
       </c>
@@ -5398,7 +5405,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -5406,7 +5413,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
         <v>64</v>
       </c>
@@ -5414,7 +5421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
         <v>65</v>
       </c>
@@ -5422,7 +5429,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
         <v>66</v>
       </c>
@@ -5430,7 +5437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
         <v>67</v>
       </c>
@@ -5438,7 +5445,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
@@ -5446,7 +5453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
@@ -5454,7 +5461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
         <v>70</v>
       </c>
@@ -5462,7 +5469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -5470,7 +5477,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
         <v>72</v>
       </c>
@@ -5478,7 +5485,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -5486,7 +5493,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
         <v>74</v>
       </c>
@@ -5494,7 +5501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
         <v>75</v>
       </c>
@@ -5502,7 +5509,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
         <v>76</v>
       </c>
@@ -5510,7 +5517,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
         <v>77</v>
       </c>
@@ -5518,7 +5525,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
         <v>78</v>
       </c>
@@ -5526,7 +5533,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -5534,7 +5541,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>97</v>
       </c>
@@ -5543,7 +5550,7 @@
         <v>38.0384615384615</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
         <v>98</v>
       </c>
@@ -5577,7 +5584,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="25.25"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5615,7 +5622,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -5662,7 +5669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
@@ -5711,7 +5718,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5758,7 +5765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
@@ -5806,7 +5813,7 @@
         <v>5.1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
@@ -5855,7 +5862,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
@@ -5904,7 +5911,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
@@ -5953,7 +5960,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>9</v>
       </c>
@@ -6001,7 +6008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>10</v>
       </c>
@@ -6050,7 +6057,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>11</v>
       </c>
@@ -6099,7 +6106,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>12</v>
       </c>
@@ -6147,7 +6154,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>13</v>
       </c>
@@ -6196,7 +6203,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
         <v>14</v>
       </c>
@@ -6243,7 +6250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
         <v>15</v>
       </c>
@@ -6292,7 +6299,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
         <v>16</v>
       </c>
@@ -6341,7 +6348,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
         <v>17</v>
       </c>
@@ -6389,7 +6396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
         <v>18</v>
       </c>
@@ -6438,7 +6445,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
         <v>19</v>
       </c>
@@ -6487,7 +6494,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
         <v>20</v>
       </c>
@@ -6536,7 +6543,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
         <v>21</v>
       </c>
@@ -6585,7 +6592,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
         <v>22</v>
       </c>
@@ -6633,7 +6640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
         <v>23</v>
       </c>
@@ -6682,7 +6689,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
         <v>24</v>
       </c>
@@ -6731,7 +6738,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
         <v>25</v>
       </c>
@@ -6780,7 +6787,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
         <v>26</v>
       </c>
@@ -6827,7 +6834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
         <v>27</v>
       </c>
@@ -6868,15 +6875,17 @@
         <v>9.9</v>
       </c>
       <c r="K27" s="2" t="n">
-        <f aca="false">'Prova 1'!B27/10</f>
         <v>8.3</v>
       </c>
       <c r="L27" s="10" t="n">
         <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D27*0.2,G27*0.05,J27*0.05,K27)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>9.5</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M27" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
         <v>28</v>
       </c>
@@ -6925,7 +6934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
         <v>96</v>
       </c>
@@ -6974,7 +6983,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
         <v>30</v>
       </c>
@@ -7023,7 +7032,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
         <v>31</v>
       </c>
@@ -7071,7 +7080,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
         <v>32</v>
       </c>
@@ -7120,7 +7129,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
         <v>33</v>
       </c>
@@ -7169,7 +7178,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
         <v>34</v>
       </c>
@@ -7218,7 +7227,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
         <v>35</v>
       </c>
@@ -7265,7 +7274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
         <v>36</v>
       </c>
@@ -7313,7 +7322,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
         <v>37</v>
       </c>
@@ -7362,7 +7371,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
         <v>38</v>
       </c>
@@ -7411,7 +7420,7 @@
         <v>9.7</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
         <v>39</v>
       </c>
@@ -7458,7 +7467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
         <v>40</v>
       </c>
@@ -7507,7 +7516,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
         <v>41</v>
       </c>
@@ -7556,7 +7565,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
         <v>42</v>
       </c>
@@ -7605,7 +7614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
         <v>43</v>
       </c>
@@ -7654,7 +7663,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
         <v>44</v>
       </c>
@@ -7703,7 +7712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
         <v>45</v>
       </c>
@@ -7752,7 +7761,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
         <v>46</v>
       </c>
@@ -7801,7 +7810,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
         <v>47</v>
       </c>
@@ -7846,10 +7855,10 @@
         <v>8.4</v>
       </c>
       <c r="M47" s="11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
         <v>48</v>
       </c>
@@ -7898,7 +7907,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
         <v>49</v>
       </c>
@@ -7946,7 +7955,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
         <v>50</v>
       </c>
@@ -7995,7 +8004,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
         <v>51</v>
       </c>
@@ -8044,7 +8053,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
         <v>52</v>
       </c>
@@ -8093,7 +8102,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
         <v>53</v>
       </c>
@@ -8142,7 +8151,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
         <v>54</v>
       </c>
@@ -8189,10 +8198,10 @@
         <v>6.7</v>
       </c>
       <c r="M54" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
         <v>55</v>
       </c>
@@ -8241,7 +8250,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
         <v>56</v>
       </c>
@@ -8290,7 +8299,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
         <v>57</v>
       </c>
@@ -8339,7 +8348,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
         <v>58</v>
       </c>
@@ -8388,7 +8397,7 @@
         <v>8.2</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
         <v>59</v>
       </c>
@@ -8437,7 +8446,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
         <v>60</v>
       </c>
@@ -8486,7 +8495,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9" t="s">
         <v>61</v>
       </c>
@@ -8535,7 +8544,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
         <v>62</v>
       </c>
@@ -8584,7 +8593,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
         <v>63</v>
       </c>
@@ -8633,7 +8642,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
         <v>64</v>
       </c>
@@ -8680,7 +8689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
         <v>65</v>
       </c>
@@ -8729,7 +8738,7 @@
         <v>9.7</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
         <v>66</v>
       </c>
@@ -8778,7 +8787,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
         <v>67</v>
       </c>
@@ -8827,7 +8836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
         <v>68</v>
       </c>
@@ -8875,7 +8884,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
         <v>69</v>
       </c>
@@ -8922,7 +8931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="9" t="s">
         <v>70</v>
       </c>
@@ -8971,7 +8980,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="9" t="s">
         <v>71</v>
       </c>
@@ -9020,7 +9029,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
         <v>72</v>
       </c>
@@ -9069,7 +9078,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
         <v>73</v>
       </c>
@@ -9118,7 +9127,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="s">
         <v>74</v>
       </c>
@@ -9166,7 +9175,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
         <v>75</v>
       </c>
@@ -9214,7 +9223,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
         <v>76</v>
       </c>
@@ -9263,7 +9272,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
         <v>77</v>
       </c>
@@ -9312,7 +9321,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
         <v>78</v>
       </c>
@@ -9361,7 +9370,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
         <v>79</v>
       </c>
@@ -9429,8 +9438,8 @@
   <dimension ref="A1:B79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9793,7 +9802,7 @@
       <c r="A47" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="13" t="n">
+      <c r="B47" s="2" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -9849,7 +9858,7 @@
       <c r="A54" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="13" t="n">
+      <c r="B54" s="2" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -10058,4 +10067,643 @@
     <oddFooter>&amp;C&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B79"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.02"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Notas_EDO_IMPA_TECH.xlsx
+++ b/Notas_EDO_IMPA_TECH.xlsx
@@ -502,7 +502,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -552,6 +552,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10077,8 +10081,8 @@
   <dimension ref="A1:B79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.02"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10100,7 +10104,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10121,14 +10125,16 @@
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="13" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10152,7 +10158,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10168,7 +10174,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10176,7 +10182,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10190,7 +10196,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10206,7 +10212,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10214,7 +10220,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10230,7 +10236,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10238,7 +10244,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10246,7 +10252,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10254,7 +10260,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10262,7 +10268,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10284,7 +10290,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10292,7 +10298,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10308,7 +10314,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10316,7 +10322,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10332,7 +10338,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10362,7 +10368,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10378,7 +10384,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10386,7 +10392,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10394,7 +10400,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10410,7 +10416,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10418,7 +10424,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10426,7 +10432,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10466,7 +10472,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10474,7 +10480,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10482,7 +10488,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10490,7 +10496,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10498,7 +10504,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10506,7 +10512,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>0.1</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10514,7 +10520,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10522,7 +10528,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10570,7 +10576,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10584,7 +10590,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10592,7 +10598,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10600,7 +10606,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10630,7 +10636,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10638,7 +10644,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10646,7 +10652,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10662,7 +10668,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10670,7 +10676,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10678,7 +10684,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Notas_EDO_IMPA_TECH.xlsx
+++ b/Notas_EDO_IMPA_TECH.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Teste 1" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="118">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -359,13 +359,28 @@
     <t xml:space="preserve">AV1</t>
   </si>
   <si>
+    <t xml:space="preserve">OBS: +0.3 na AV2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS: +0.4 na AV2</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS: +0.7 na AV2 (se nota(AV2) &gt; 9.7, nota final = 10) </t>
   </si>
   <si>
+    <t xml:space="preserve">OBS: +0.2 na AV2</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS: +0.7 na AV2</t>
   </si>
   <si>
+    <t xml:space="preserve">OBS: +0.8 na AV2</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS: +0.5 na AV2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS: +0.6 na AV2</t>
   </si>
 </sst>
 </file>
@@ -543,7 +558,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -552,10 +571,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4934,7 +4949,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5078,7 +5093,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5270,7 +5285,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5310,7 +5325,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5326,7 +5341,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5342,7 +5357,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5350,7 +5365,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5358,7 +5373,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5398,7 +5413,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5406,7 +5421,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5551,7 +5566,7 @@
       </c>
       <c r="B80" s="2" t="n">
         <f aca="false">AVERAGE(B2:B79)</f>
-        <v>38.0384615384615</v>
+        <v>38.8205128205128</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5560,7 +5575,7 @@
       </c>
       <c r="B81" s="2" t="n">
         <f aca="false">STDEV(B2:B79)</f>
-        <v>26.1560960130016</v>
+        <v>26.4505142413093</v>
       </c>
     </row>
   </sheetData>
@@ -5715,11 +5730,13 @@
       </c>
       <c r="K3" s="2" t="n">
         <f aca="false">'Prova 1'!B3/10</f>
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="L3" s="10" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D3*0.2,G3*0.05,J3*0.05,K3)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>6</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6589,11 +6606,13 @@
       </c>
       <c r="K21" s="2" t="n">
         <f aca="false">'Prova 1'!B21/10</f>
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="L21" s="10" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D21*0.2,G21*0.05,J21*0.05,K21)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>6.3</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6885,8 +6904,8 @@
         <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D27*0.2,G27*0.05,J27*0.05,K27)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>9.5</v>
       </c>
-      <c r="M27" s="11" t="s">
-        <v>110</v>
+      <c r="M27" s="12" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7758,11 +7777,13 @@
       </c>
       <c r="K45" s="2" t="n">
         <f aca="false">'Prova 1'!B45/10</f>
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="L45" s="10" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D45*0.2,G45*0.05,J45*0.05,K45)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>6.3</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7858,8 +7879,8 @@
       <c r="L47" s="10" t="n">
         <v>8.4</v>
       </c>
-      <c r="M47" s="11" t="s">
-        <v>111</v>
+      <c r="M47" s="12" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7906,7 +7927,7 @@
         <f aca="false">'Prova 1'!B48/10</f>
         <v>1.2</v>
       </c>
-      <c r="L48" s="12" t="n">
+      <c r="L48" s="13" t="n">
         <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D48*0.2,G48*0.05,J48*0.05,K48)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>5.3</v>
       </c>
@@ -8001,11 +8022,13 @@
       </c>
       <c r="K50" s="2" t="n">
         <f aca="false">'Prova 1'!B50/10</f>
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="L50" s="10" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D50*0.2,G50*0.05,J50*0.05,K50)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>7.3</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8099,11 +8122,13 @@
       </c>
       <c r="K52" s="2" t="n">
         <f aca="false">'Prova 1'!B52/10</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L52" s="8" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D52*0.2,G52*0.05,J52*0.05,K52)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>5.7</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8196,13 +8221,13 @@
       </c>
       <c r="K54" s="2" t="n">
         <f aca="false">'Prova 1'!B54/10</f>
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L54" s="10" t="n">
         <v>6.7</v>
       </c>
-      <c r="M54" s="11" t="s">
-        <v>112</v>
+      <c r="M54" s="12" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8247,11 +8272,13 @@
       </c>
       <c r="K55" s="2" t="n">
         <f aca="false">'Prova 1'!B55/10</f>
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="L55" s="10" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D55*0.2,G55*0.05,J55*0.05,K55)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>8.4</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8296,11 +8323,13 @@
       </c>
       <c r="K56" s="2" t="n">
         <f aca="false">'Prova 1'!B56/10</f>
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L56" s="10" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D56*0.2,G56*0.05,J56*0.05,K56)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>7.5</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8541,11 +8570,13 @@
       </c>
       <c r="K61" s="2" t="n">
         <f aca="false">'Prova 1'!B61/10</f>
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="L61" s="10" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D61*0.2,G61*0.05,J61*0.05,K61)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>8.4</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8590,11 +8621,13 @@
       </c>
       <c r="K62" s="2" t="n">
         <f aca="false">'Prova 1'!B62/10</f>
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="L62" s="10" t="n">
-        <f aca="false">_xlfn.FLOOR.MATH(10*((SUM(D62*0.2,G62*0.05,J62*0.05,K62)*(6/5))*(20/43) + (138/43)))/10</f>
         <v>8.6</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10125,7 +10158,7 @@
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="2" t="n">
         <v>0.1</v>
       </c>
     </row>
